--- a/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -726,13 +726,13 @@
         <v>1100</v>
       </c>
       <c r="G8" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="H8" s="3">
         <v>1600</v>
       </c>
       <c r="I8" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="J8" s="3">
         <v>1200</v>
@@ -755,7 +755,7 @@
         <v>300</v>
       </c>
       <c r="G9" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H9" s="3">
         <v>400</v>
@@ -820,7 +820,7 @@
         <v>1000</v>
       </c>
       <c r="E12" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="F12" s="3">
         <v>700</v>
@@ -946,7 +946,7 @@
         <v>3100</v>
       </c>
       <c r="E17" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="F17" s="3">
         <v>2400</v>
@@ -972,10 +972,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="E18" s="3">
-        <v>-2100</v>
+        <v>-2200</v>
       </c>
       <c r="F18" s="3">
         <v>-1300</v>
@@ -984,7 +984,7 @@
         <v>-1100</v>
       </c>
       <c r="H18" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="I18" s="3">
         <v>-800</v>
@@ -1104,10 +1104,10 @@
         <v>-1300</v>
       </c>
       <c r="E23" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F23" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="G23" s="3">
         <v>-1400</v>
@@ -1194,7 +1194,7 @@
         <v>1000</v>
       </c>
       <c r="F26" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="G26" s="3">
         <v>-1400</v>
@@ -1223,7 +1223,7 @@
         <v>1000</v>
       </c>
       <c r="F27" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="G27" s="3">
         <v>-1400</v>
@@ -1397,7 +1397,7 @@
         <v>1000</v>
       </c>
       <c r="F33" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="G33" s="3">
         <v>-1400</v>
@@ -1455,7 +1455,7 @@
         <v>1000</v>
       </c>
       <c r="F35" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="G35" s="3">
         <v>-1400</v>
@@ -1538,10 +1538,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>10300</v>
+        <v>10500</v>
       </c>
       <c r="E41" s="3">
-        <v>12200</v>
+        <v>12400</v>
       </c>
       <c r="F41" s="3">
         <v>1500</v>
@@ -1550,7 +1550,7 @@
         <v>2600</v>
       </c>
       <c r="H41" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="I41" s="3">
         <v>1600</v>
@@ -1611,7 +1611,7 @@
         <v>500</v>
       </c>
       <c r="I43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J43" s="3">
         <v>400</v>
@@ -1628,7 +1628,7 @@
         <v>700</v>
       </c>
       <c r="E44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F44" s="3">
         <v>500</v>
@@ -1683,10 +1683,10 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11500</v>
+        <v>11700</v>
       </c>
       <c r="E46" s="3">
-        <v>13400</v>
+        <v>13600</v>
       </c>
       <c r="F46" s="3">
         <v>2700</v>
@@ -1701,7 +1701,7 @@
         <v>2400</v>
       </c>
       <c r="J46" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="K46" s="3">
         <v>4200</v>
@@ -1915,19 +1915,19 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11800</v>
+        <v>12000</v>
       </c>
       <c r="E54" s="3">
-        <v>13700</v>
+        <v>14000</v>
       </c>
       <c r="F54" s="3">
         <v>3100</v>
       </c>
       <c r="G54" s="3">
-        <v>3800</v>
+        <v>3900</v>
       </c>
       <c r="H54" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="I54" s="3">
         <v>3000</v>
@@ -1973,13 +1973,13 @@
         <v>1300</v>
       </c>
       <c r="E57" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F57" s="3">
         <v>1200</v>
       </c>
       <c r="G57" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H57" s="3">
         <v>800</v>
@@ -2066,7 +2066,7 @@
         <v>1400</v>
       </c>
       <c r="G60" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H60" s="3">
         <v>1000</v>
@@ -2231,7 +2231,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="E66" s="3">
         <v>2200</v>
@@ -2246,7 +2246,7 @@
         <v>1700</v>
       </c>
       <c r="I66" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="J66" s="3">
         <v>1800</v>
@@ -2389,25 +2389,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-17300</v>
+        <v>-17600</v>
       </c>
       <c r="E72" s="3">
-        <v>-15400</v>
+        <v>-15600</v>
       </c>
       <c r="F72" s="3">
-        <v>-16100</v>
+        <v>-16400</v>
       </c>
       <c r="G72" s="3">
-        <v>-15000</v>
+        <v>-15200</v>
       </c>
       <c r="H72" s="3">
-        <v>-13900</v>
+        <v>-14100</v>
       </c>
       <c r="I72" s="3">
-        <v>-13500</v>
+        <v>-13700</v>
       </c>
       <c r="J72" s="3">
-        <v>-12700</v>
+        <v>-12900</v>
       </c>
       <c r="K72" s="3">
         <v>-11900</v>
@@ -2505,10 +2505,10 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9600</v>
+        <v>9800</v>
       </c>
       <c r="E76" s="3">
-        <v>11600</v>
+        <v>11800</v>
       </c>
       <c r="F76" s="3">
         <v>1000</v>
@@ -2523,7 +2523,7 @@
         <v>1300</v>
       </c>
       <c r="J76" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="K76" s="3">
         <v>2900</v>
@@ -2603,7 +2603,7 @@
         <v>1000</v>
       </c>
       <c r="F81" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="G81" s="3">
         <v>-1400</v>
@@ -2816,7 +2816,7 @@
         <v>-1500</v>
       </c>
       <c r="E89" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="F89" s="3">
         <v>-900</v>
@@ -3103,16 +3103,16 @@
         <v>-100</v>
       </c>
       <c r="E100" s="3">
-        <v>12800</v>
+        <v>13000</v>
       </c>
       <c r="F100" s="3">
         <v>-200</v>
       </c>
       <c r="G100" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="H100" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
@@ -3158,19 +3158,19 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="E102" s="3">
-        <v>10800</v>
+        <v>11000</v>
       </c>
       <c r="F102" s="3">
         <v>-1100</v>
       </c>
       <c r="G102" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="H102" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="I102" s="3">
         <v>-800</v>

--- a/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>MOB</t>
   </si>
@@ -656,150 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E8" s="3">
         <v>800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1100</v>
       </c>
       <c r="F8" s="3">
         <v>1100</v>
       </c>
       <c r="G8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H8" s="3">
         <v>1300</v>
       </c>
-      <c r="H8" s="3">
-        <v>1600</v>
-      </c>
       <c r="I8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J8" s="3">
         <v>900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="E9" s="3">
         <v>200</v>
       </c>
       <c r="F9" s="3">
+        <v>200</v>
+      </c>
+      <c r="G9" s="3">
         <v>300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>400</v>
       </c>
       <c r="H9" s="3">
         <v>400</v>
       </c>
       <c r="I9" s="3">
+        <v>400</v>
+      </c>
+      <c r="J9" s="3">
         <v>200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>300</v>
       </c>
       <c r="K9" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="3">
         <v>600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -811,8 +824,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,25 +837,28 @@
         <v>1000</v>
       </c>
       <c r="F12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="3">
         <v>700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>800</v>
-      </c>
-      <c r="H12" s="3">
-        <v>700</v>
       </c>
       <c r="I12" s="3">
         <v>700</v>
       </c>
       <c r="J12" s="3">
+        <v>700</v>
+      </c>
+      <c r="K12" s="3">
         <v>900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -869,8 +886,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -898,8 +918,11 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -927,8 +950,11 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -937,66 +963,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>3100</v>
+        <v>4000</v>
       </c>
       <c r="E17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F17" s="3">
         <v>3300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2400</v>
       </c>
       <c r="G17" s="3">
         <v>2400</v>
       </c>
       <c r="H17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-1100</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-800</v>
       </c>
       <c r="J18" s="3">
         <v>-800</v>
       </c>
       <c r="K18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1008,37 +1041,41 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1066,8 +1103,11 @@
       <c r="K21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1080,61 +1120,67 @@
       <c r="F22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G23" s="3">
         <v>-1300</v>
       </c>
-      <c r="E23" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1153,8 +1199,11 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1182,66 +1231,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1400</v>
       </c>
-      <c r="E26" s="3">
-        <v>1000</v>
-      </c>
       <c r="F26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1400</v>
       </c>
-      <c r="E27" s="3">
-        <v>1000</v>
-      </c>
       <c r="F27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G27" s="3">
         <v>-1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1269,8 +1327,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1298,8 +1359,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1327,8 +1391,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1356,66 +1423,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1400</v>
       </c>
-      <c r="E33" s="3">
-        <v>1000</v>
-      </c>
       <c r="F33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G33" s="3">
         <v>-1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1443,71 +1519,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1400</v>
       </c>
-      <c r="E35" s="3">
-        <v>1000</v>
-      </c>
       <c r="F35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G35" s="3">
         <v>-1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1519,8 +1604,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1532,37 +1618,41 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>10500</v>
+        <v>8200</v>
       </c>
       <c r="E41" s="3">
-        <v>12400</v>
+        <v>10600</v>
       </c>
       <c r="F41" s="3">
+        <v>12600</v>
+      </c>
+      <c r="G41" s="3">
         <v>1500</v>
       </c>
-      <c r="G41" s="3">
-        <v>2600</v>
-      </c>
       <c r="H41" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I41" s="3">
         <v>3600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1590,66 +1680,75 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="E43" s="3">
         <v>500</v>
       </c>
       <c r="F43" s="3">
+        <v>600</v>
+      </c>
+      <c r="G43" s="3">
         <v>300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>500</v>
       </c>
       <c r="H43" s="3">
         <v>500</v>
       </c>
       <c r="I43" s="3">
+        <v>500</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>900</v>
+      </c>
+      <c r="E44" s="3">
         <v>700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>400</v>
-      </c>
-      <c r="I44" s="3">
-        <v>500</v>
       </c>
       <c r="J44" s="3">
         <v>500</v>
       </c>
       <c r="K44" s="3">
+        <v>500</v>
+      </c>
+      <c r="L44" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1657,13 +1756,13 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>16</v>
@@ -1677,37 +1776,43 @@
       <c r="K45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11700</v>
+        <v>10100</v>
       </c>
       <c r="E46" s="3">
-        <v>13600</v>
+        <v>11900</v>
       </c>
       <c r="F46" s="3">
+        <v>13800</v>
+      </c>
+      <c r="G46" s="3">
         <v>2700</v>
       </c>
-      <c r="G46" s="3">
-        <v>3400</v>
-      </c>
       <c r="H46" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I46" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J46" s="3">
         <v>2400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1735,37 +1840,43 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>500</v>
+      </c>
+      <c r="E48" s="3">
         <v>300</v>
-      </c>
-      <c r="E48" s="3">
-        <v>400</v>
       </c>
       <c r="F48" s="3">
         <v>400</v>
       </c>
       <c r="G48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H48" s="3">
         <v>500</v>
       </c>
       <c r="I48" s="3">
+        <v>500</v>
+      </c>
+      <c r="J48" s="3">
         <v>600</v>
-      </c>
-      <c r="J48" s="3">
-        <v>700</v>
       </c>
       <c r="K48" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1793,8 +1904,11 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1822,8 +1936,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1851,8 +1968,11 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -1880,8 +2000,11 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1909,37 +2032,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>12000</v>
+        <v>10600</v>
       </c>
       <c r="E54" s="3">
-        <v>14000</v>
+        <v>12200</v>
       </c>
       <c r="F54" s="3">
-        <v>3100</v>
+        <v>14100</v>
       </c>
       <c r="G54" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I54" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K54" s="3">
         <v>3900</v>
       </c>
-      <c r="H54" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I54" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J54" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1951,8 +2080,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1964,37 +2094,41 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
-        <v>1200</v>
-      </c>
       <c r="G57" s="3">
-        <v>800</v>
+        <v>1300</v>
       </c>
       <c r="H57" s="3">
         <v>800</v>
       </c>
       <c r="I57" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J57" s="3">
         <v>700</v>
       </c>
       <c r="K57" s="3">
+        <v>700</v>
+      </c>
+      <c r="L57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2020,21 +2154,24 @@
         <v>200</v>
       </c>
       <c r="K58" s="3">
+        <v>200</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>700</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>16</v>
@@ -2051,42 +2188,48 @@
       <c r="K59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F60" s="3">
         <v>2000</v>
       </c>
-      <c r="E60" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1400</v>
-      </c>
       <c r="G60" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="H60" s="3">
         <v>1000</v>
       </c>
       <c r="I60" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="J60" s="3">
         <v>900</v>
       </c>
       <c r="K60" s="3">
+        <v>900</v>
+      </c>
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
@@ -2095,33 +2238,36 @@
         <v>100</v>
       </c>
       <c r="G61" s="3">
+        <v>100</v>
+      </c>
+      <c r="H61" s="3">
         <v>200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>300</v>
-      </c>
-      <c r="I61" s="3">
-        <v>400</v>
       </c>
       <c r="J61" s="3">
         <v>400</v>
       </c>
       <c r="K61" s="3">
+        <v>400</v>
+      </c>
+      <c r="L61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
       </c>
       <c r="F62" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G62" s="3">
         <v>500</v>
@@ -2138,8 +2284,11 @@
       <c r="K62" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2167,8 +2316,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2196,8 +2348,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2225,37 +2380,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1700</v>
       </c>
       <c r="H66" s="3">
         <v>1700</v>
       </c>
       <c r="I66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J66" s="3">
         <v>1700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2267,8 +2428,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2296,8 +2458,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2325,8 +2490,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2354,8 +2522,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2383,37 +2554,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-17600</v>
+        <v>-20300</v>
       </c>
       <c r="E72" s="3">
-        <v>-15600</v>
+        <v>-17800</v>
       </c>
       <c r="F72" s="3">
-        <v>-16400</v>
+        <v>-15800</v>
       </c>
       <c r="G72" s="3">
-        <v>-15200</v>
+        <v>-16600</v>
       </c>
       <c r="H72" s="3">
-        <v>-14100</v>
+        <v>-15400</v>
       </c>
       <c r="I72" s="3">
-        <v>-13700</v>
+        <v>-14300</v>
       </c>
       <c r="J72" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="K72" s="3">
         <v>-12900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2441,8 +2618,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2470,8 +2650,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2499,37 +2682,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9800</v>
+        <v>7500</v>
       </c>
       <c r="E76" s="3">
-        <v>11800</v>
+        <v>9900</v>
       </c>
       <c r="F76" s="3">
+        <v>11900</v>
+      </c>
+      <c r="G76" s="3">
         <v>1000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2200</v>
       </c>
-      <c r="H76" s="3">
-        <v>3300</v>
-      </c>
       <c r="I76" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J76" s="3">
         <v>1300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2557,71 +2746,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1400</v>
       </c>
-      <c r="E81" s="3">
-        <v>1000</v>
-      </c>
       <c r="F81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G81" s="3">
         <v>-1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2633,8 +2831,9 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2662,8 +2861,11 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2691,8 +2893,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2720,8 +2925,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2749,8 +2957,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2778,8 +2989,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2807,37 +3021,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2849,8 +3069,9 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2878,8 +3099,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2907,8 +3131,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2936,8 +3163,11 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -2963,10 +3193,13 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2978,8 +3211,9 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3007,8 +3241,11 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3036,8 +3273,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3065,8 +3305,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3094,8 +3337,11 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3103,46 +3349,49 @@
         <v>-100</v>
       </c>
       <c r="E100" s="3">
-        <v>13000</v>
+        <v>-100</v>
       </c>
       <c r="F100" s="3">
-        <v>-200</v>
+        <v>13200</v>
       </c>
       <c r="G100" s="3">
         <v>-200</v>
       </c>
       <c r="H100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I100" s="3">
         <v>2400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="F101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="H101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
@@ -3152,33 +3401,39 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
-        <v>11000</v>
-      </c>
       <c r="F102" s="3">
-        <v>-1100</v>
+        <v>11100</v>
       </c>
       <c r="G102" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
@@ -803,7 +803,7 @@
         <v>1200</v>
       </c>
       <c r="J10" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="K10" s="3">
         <v>900</v>
@@ -1054,7 +1054,7 @@
         <v>1000</v>
       </c>
       <c r="F20" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E23" s="3">
         <v>-1400</v>
@@ -1240,7 +1240,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E26" s="3">
         <v>-1400</v>
@@ -1272,7 +1272,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E27" s="3">
         <v>-1400</v>
@@ -1438,7 +1438,7 @@
         <v>-1000</v>
       </c>
       <c r="F32" s="3">
-        <v>-3200</v>
+        <v>-3300</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E33" s="3">
         <v>-1400</v>
@@ -1528,7 +1528,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E35" s="3">
         <v>-1400</v>
@@ -1628,10 +1628,10 @@
         <v>8200</v>
       </c>
       <c r="E41" s="3">
-        <v>10600</v>
+        <v>10700</v>
       </c>
       <c r="F41" s="3">
-        <v>12600</v>
+        <v>12700</v>
       </c>
       <c r="G41" s="3">
         <v>1500</v>
@@ -1640,10 +1640,10 @@
         <v>2700</v>
       </c>
       <c r="I41" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="J41" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="K41" s="3">
         <v>2400</v>
@@ -1794,7 +1794,7 @@
         <v>13800</v>
       </c>
       <c r="G46" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="H46" s="3">
         <v>3500</v>
@@ -2041,13 +2041,13 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10600</v>
+        <v>10700</v>
       </c>
       <c r="E54" s="3">
-        <v>12200</v>
+        <v>12300</v>
       </c>
       <c r="F54" s="3">
-        <v>14100</v>
+        <v>14200</v>
       </c>
       <c r="G54" s="3">
         <v>3200</v>
@@ -2056,10 +2056,10 @@
         <v>4000</v>
       </c>
       <c r="I54" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="J54" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="K54" s="3">
         <v>3900</v>
@@ -2165,7 +2165,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E59" s="3">
         <v>600</v>
@@ -2197,7 +2197,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="E60" s="3">
         <v>2100</v>
@@ -2264,7 +2264,7 @@
         <v>200</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F62" s="3">
         <v>100</v>
@@ -2273,7 +2273,7 @@
         <v>500</v>
       </c>
       <c r="H62" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I62" s="3">
         <v>500</v>
@@ -2401,7 +2401,7 @@
         <v>2100</v>
       </c>
       <c r="H66" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="I66" s="3">
         <v>1800</v>
@@ -2563,25 +2563,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-20300</v>
+        <v>-20500</v>
       </c>
       <c r="E72" s="3">
-        <v>-17800</v>
+        <v>-18000</v>
       </c>
       <c r="F72" s="3">
-        <v>-15800</v>
+        <v>-15900</v>
       </c>
       <c r="G72" s="3">
-        <v>-16600</v>
+        <v>-16700</v>
       </c>
       <c r="H72" s="3">
-        <v>-15400</v>
+        <v>-15500</v>
       </c>
       <c r="I72" s="3">
-        <v>-14300</v>
+        <v>-14400</v>
       </c>
       <c r="J72" s="3">
-        <v>-13900</v>
+        <v>-14000</v>
       </c>
       <c r="K72" s="3">
         <v>-12900</v>
@@ -2691,13 +2691,13 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="E76" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="F76" s="3">
-        <v>11900</v>
+        <v>12000</v>
       </c>
       <c r="G76" s="3">
         <v>1000</v>
@@ -2709,7 +2709,7 @@
         <v>3400</v>
       </c>
       <c r="J76" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="K76" s="3">
         <v>2200</v>
@@ -2792,7 +2792,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E81" s="3">
         <v>-1400</v>
@@ -3352,7 +3352,7 @@
         <v>-100</v>
       </c>
       <c r="F100" s="3">
-        <v>13200</v>
+        <v>13300</v>
       </c>
       <c r="G100" s="3">
         <v>-200</v>
@@ -3410,13 +3410,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="E102" s="3">
         <v>-2000</v>
       </c>
       <c r="F102" s="3">
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="G102" s="3">
         <v>-1200</v>

--- a/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>MOB</t>
   </si>
@@ -656,163 +656,188 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1900</v>
+        <v>900</v>
       </c>
       <c r="E8" s="3">
+        <v>900</v>
+      </c>
+      <c r="F8" s="3">
+        <v>900</v>
+      </c>
+      <c r="G8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1100</v>
-      </c>
       <c r="H8" s="3">
+        <v>300</v>
+      </c>
+      <c r="I8" s="3">
+        <v>300</v>
+      </c>
+      <c r="J8" s="3">
+        <v>400</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L8" s="3">
+        <v>900</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N8" s="3">
         <v>1300</v>
       </c>
-      <c r="I8" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J8" s="3">
-        <v>900</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="E9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G9" s="3">
         <v>300</v>
       </c>
       <c r="H9" s="3">
+        <v>100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>100</v>
+      </c>
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
-        <v>400</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>200</v>
+      </c>
+      <c r="K10" s="3">
         <v>1200</v>
       </c>
-      <c r="E10" s="3">
-        <v>600</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="L10" s="3">
+        <v>700</v>
+      </c>
+      <c r="M10" s="3">
         <v>900</v>
       </c>
-      <c r="G10" s="3">
-        <v>800</v>
-      </c>
-      <c r="H10" s="3">
-        <v>900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>700</v>
-      </c>
-      <c r="K10" s="3">
-        <v>900</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -825,40 +850,48 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E12" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F12" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G12" s="3">
+        <v>500</v>
+      </c>
+      <c r="H12" s="3">
+        <v>500</v>
+      </c>
+      <c r="I12" s="3">
+        <v>500</v>
+      </c>
+      <c r="J12" s="3">
+        <v>500</v>
+      </c>
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
-        <v>800</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="J12" s="3">
-        <v>700</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,31 +922,37 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -921,16 +960,22 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -939,10 +984,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -953,8 +998,14 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -964,72 +1015,86 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>4000</v>
+        <v>1300</v>
       </c>
       <c r="E17" s="3">
-        <v>3200</v>
+        <v>1300</v>
       </c>
       <c r="F17" s="3">
-        <v>3300</v>
+        <v>2100</v>
       </c>
       <c r="G17" s="3">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="H17" s="3">
-        <v>2400</v>
+        <v>1500</v>
       </c>
       <c r="I17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K17" s="3">
         <v>2100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-2200</v>
+        <v>-400</v>
       </c>
       <c r="E18" s="3">
-        <v>-2400</v>
+        <v>-400</v>
       </c>
       <c r="F18" s="3">
-        <v>-2200</v>
+        <v>-1200</v>
       </c>
       <c r="G18" s="3">
-        <v>-1300</v>
+        <v>-1200</v>
       </c>
       <c r="H18" s="3">
         <v>-1200</v>
       </c>
       <c r="I18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1042,63 +1107,71 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-1000</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>1000</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>3300</v>
+        <v>400</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K20" s="3">
+        <v>100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>16</v>
+      <c r="D21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>16</v>
@@ -1106,22 +1179,28 @@
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>16</v>
+      <c r="D22" s="3">
+        <v>500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>500</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1129,49 +1208,61 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-3200</v>
+        <v>-800</v>
       </c>
       <c r="E23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>500</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N23" s="3">
         <v>-1400</v>
       </c>
-      <c r="F23" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-800</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-1400</v>
-      </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1179,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1202,8 +1293,14 @@
       <c r="L24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1234,72 +1331,90 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3200</v>
+        <v>-800</v>
       </c>
       <c r="E26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>500</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="F26" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-800</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-1400</v>
-      </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3200</v>
+        <v>-800</v>
       </c>
       <c r="E27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J27" s="3">
+        <v>500</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N27" s="3">
         <v>-1400</v>
       </c>
-      <c r="F27" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-800</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-1400</v>
-      </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1330,8 +1445,14 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1362,8 +1483,14 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1394,8 +1521,14 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1426,72 +1559,90 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>-1000</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>-3300</v>
+        <v>-400</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="H32" s="3">
+        <v>500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3200</v>
+        <v>-800</v>
       </c>
       <c r="E33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J33" s="3">
+        <v>500</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N33" s="3">
         <v>-1400</v>
       </c>
-      <c r="F33" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-800</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-1400</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1522,77 +1673,95 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3200</v>
+        <v>-800</v>
       </c>
       <c r="E35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J35" s="3">
+        <v>500</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N35" s="3">
         <v>-1400</v>
       </c>
-      <c r="F35" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-800</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-1400</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1605,8 +1774,10 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1619,40 +1790,48 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8200</v>
+        <v>9700</v>
       </c>
       <c r="E41" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G41" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H41" s="3">
+        <v>10600</v>
+      </c>
+      <c r="I41" s="3">
         <v>10700</v>
       </c>
-      <c r="F41" s="3">
-        <v>12700</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H41" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K41" s="3">
         <v>3700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1683,22 +1862,28 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1000</v>
       </c>
-      <c r="E43" s="3">
-        <v>500</v>
-      </c>
-      <c r="F43" s="3">
-        <v>600</v>
-      </c>
       <c r="G43" s="3">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="H43" s="3">
         <v>500</v>
@@ -1707,62 +1892,74 @@
         <v>500</v>
       </c>
       <c r="J43" s="3">
+        <v>600</v>
+      </c>
+      <c r="K43" s="3">
+        <v>500</v>
+      </c>
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="E44" s="3">
         <v>700</v>
       </c>
       <c r="F44" s="3">
+        <v>900</v>
+      </c>
+      <c r="G44" s="3">
+        <v>900</v>
+      </c>
+      <c r="H44" s="3">
+        <v>700</v>
+      </c>
+      <c r="I44" s="3">
+        <v>700</v>
+      </c>
+      <c r="J44" s="3">
         <v>600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
+        <v>400</v>
+      </c>
+      <c r="L44" s="3">
         <v>500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="M44" s="3">
+        <v>500</v>
+      </c>
+      <c r="N44" s="3">
         <v>300</v>
       </c>
-      <c r="I44" s="3">
-        <v>400</v>
-      </c>
-      <c r="J44" s="3">
-        <v>500</v>
-      </c>
-      <c r="K44" s="3">
-        <v>500</v>
-      </c>
-      <c r="L44" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>500</v>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>16</v>
@@ -1779,63 +1976,75 @@
       <c r="L45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10100</v>
+        <v>10900</v>
       </c>
       <c r="E46" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="G46" s="3">
+        <v>9800</v>
+      </c>
+      <c r="H46" s="3">
         <v>11900</v>
       </c>
-      <c r="F46" s="3">
-        <v>13800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H46" s="3">
-        <v>3500</v>
-      </c>
       <c r="I46" s="3">
+        <v>11900</v>
+      </c>
+      <c r="J46" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K46" s="3">
         <v>4600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1843,40 +2052,52 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>400</v>
+      </c>
+      <c r="F48" s="3">
         <v>500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
+        <v>500</v>
+      </c>
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
+        <v>300</v>
+      </c>
+      <c r="J48" s="3">
         <v>400</v>
       </c>
-      <c r="G48" s="3">
-        <v>400</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>500</v>
       </c>
-      <c r="I48" s="3">
-        <v>500</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1907,8 +2128,14 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1939,8 +2166,14 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1971,31 +2204,37 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2003,8 +2242,14 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2035,40 +2280,52 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>10700</v>
+        <v>11300</v>
       </c>
       <c r="E54" s="3">
+        <v>11300</v>
+      </c>
+      <c r="F54" s="3">
+        <v>10900</v>
+      </c>
+      <c r="G54" s="3">
+        <v>10300</v>
+      </c>
+      <c r="H54" s="3">
+        <v>12200</v>
+      </c>
+      <c r="I54" s="3">
         <v>12300</v>
       </c>
-      <c r="F54" s="3">
-        <v>14200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H54" s="3">
-        <v>4000</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
+        <v>14400</v>
+      </c>
+      <c r="K54" s="3">
         <v>5200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2081,8 +2338,10 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2095,40 +2354,48 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1400</v>
+        <v>300</v>
       </c>
       <c r="E57" s="3">
-        <v>1300</v>
+        <v>300</v>
       </c>
       <c r="F57" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="G57" s="3">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="H57" s="3">
+        <v>400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>200</v>
+      </c>
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
-        <v>800</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2157,33 +2424,39 @@
         <v>200</v>
       </c>
       <c r="L58" s="3">
+        <v>200</v>
+      </c>
+      <c r="M58" s="3">
+        <v>200</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1100</v>
+        <v>2300</v>
       </c>
       <c r="E59" s="3">
-        <v>600</v>
+        <v>2300</v>
       </c>
       <c r="F59" s="3">
-        <v>700</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>16</v>
+        <v>2000</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1600</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>16</v>
@@ -2191,95 +2464,113 @@
       <c r="L59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F60" s="3">
         <v>2700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H60" s="3">
         <v>2100</v>
       </c>
-      <c r="F60" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K60" s="3">
         <v>1000</v>
       </c>
-      <c r="I60" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
       </c>
       <c r="F61" s="3">
+        <v>200</v>
+      </c>
+      <c r="G61" s="3">
+        <v>200</v>
+      </c>
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
-        <v>200</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
+        <v>100</v>
+      </c>
+      <c r="K61" s="3">
         <v>300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>200</v>
-      </c>
-      <c r="E62" s="3">
-        <v>200</v>
-      </c>
-      <c r="F62" s="3">
-        <v>100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>500</v>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K62" s="3">
         <v>500</v>
@@ -2287,8 +2578,14 @@
       <c r="L62" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3">
+        <v>500</v>
+      </c>
+      <c r="N62" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2319,8 +2616,14 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2351,8 +2654,14 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2383,8 +2692,14 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2392,31 +2707,37 @@
         <v>3100</v>
       </c>
       <c r="E66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="G66" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H66" s="3">
         <v>2300</v>
       </c>
-      <c r="F66" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1800</v>
-      </c>
       <c r="I66" s="3">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="J66" s="3">
-        <v>1700</v>
+        <v>2300</v>
       </c>
       <c r="K66" s="3">
         <v>1800</v>
       </c>
       <c r="L66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2429,8 +2750,10 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2461,8 +2784,14 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2493,8 +2822,14 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2525,8 +2860,14 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2557,40 +2898,52 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-20500</v>
+        <v>-24000</v>
       </c>
       <c r="E72" s="3">
-        <v>-18000</v>
+        <v>-24000</v>
       </c>
       <c r="F72" s="3">
-        <v>-15900</v>
+        <v>-21100</v>
       </c>
       <c r="G72" s="3">
-        <v>-16700</v>
+        <v>-20000</v>
       </c>
       <c r="H72" s="3">
-        <v>-15500</v>
+        <v>-17400</v>
       </c>
       <c r="I72" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-14400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-14000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-12900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2621,8 +2974,14 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2653,8 +3012,14 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2685,40 +3050,52 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7600</v>
+        <v>8200</v>
       </c>
       <c r="E76" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>7700</v>
+      </c>
+      <c r="G76" s="3">
+        <v>7300</v>
+      </c>
+      <c r="H76" s="3">
+        <v>9900</v>
+      </c>
+      <c r="I76" s="3">
         <v>10000</v>
       </c>
-      <c r="F76" s="3">
-        <v>12000</v>
-      </c>
-      <c r="G76" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
+        <v>12100</v>
+      </c>
+      <c r="K76" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L76" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M76" s="3">
         <v>2200</v>
       </c>
-      <c r="I76" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J76" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K76" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2749,77 +3126,95 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3200</v>
+        <v>-800</v>
       </c>
       <c r="E81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J81" s="3">
+        <v>500</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N81" s="3">
         <v>-1400</v>
       </c>
-      <c r="F81" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-800</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-1400</v>
-      </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2832,31 +3227,33 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -2864,8 +3261,14 @@
       <c r="L83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2896,8 +3299,14 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2928,8 +3337,14 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2960,8 +3375,14 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2992,8 +3413,14 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3024,40 +3451,52 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2600</v>
+        <v>-500</v>
       </c>
       <c r="E89" s="3">
-        <v>-1500</v>
+        <v>-500</v>
       </c>
       <c r="F89" s="3">
-        <v>-2100</v>
+        <v>-1300</v>
       </c>
       <c r="G89" s="3">
-        <v>-900</v>
+        <v>-1300</v>
       </c>
       <c r="H89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="I89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-800</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3070,8 +3509,10 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3102,8 +3543,14 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3134,8 +3581,14 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3166,8 +3619,14 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3196,10 +3655,16 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3212,31 +3677,33 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3244,8 +3711,14 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3276,8 +3749,14 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3308,8 +3787,14 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3340,57 +3825,69 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>13300</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-200</v>
-      </c>
       <c r="H100" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K100" s="3">
         <v>2400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>16</v>
+      <c r="E101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
@@ -3404,36 +3901,48 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2500</v>
+        <v>600</v>
       </c>
       <c r="E102" s="3">
-        <v>-2000</v>
+        <v>600</v>
       </c>
       <c r="F102" s="3">
-        <v>11200</v>
+        <v>-1200</v>
       </c>
       <c r="G102" s="3">
         <v>-1200</v>
       </c>
       <c r="H102" s="3">
-        <v>-1000</v>
+        <v>-1100</v>
       </c>
       <c r="I102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J102" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>MOB</t>
   </si>
@@ -656,158 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="E8" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="F8" s="3">
         <v>900</v>
       </c>
       <c r="G8" s="3">
+        <v>900</v>
+      </c>
+      <c r="H8" s="3">
         <v>800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>800</v>
+      </c>
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>300</v>
+      </c>
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>300</v>
-      </c>
-      <c r="H9" s="3">
-        <v>100</v>
-      </c>
-      <c r="I9" s="3">
-        <v>100</v>
       </c>
       <c r="J9" s="3">
         <v>100</v>
       </c>
       <c r="K9" s="3">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3">
+        <v>100</v>
+      </c>
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E10" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F10" s="3">
         <v>500</v>
@@ -816,28 +835,34 @@
         <v>500</v>
       </c>
       <c r="H10" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I10" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="J10" s="3">
         <v>200</v>
       </c>
       <c r="K10" s="3">
+        <v>200</v>
+      </c>
+      <c r="L10" s="3">
+        <v>200</v>
+      </c>
+      <c r="M10" s="3">
         <v>1200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -852,8 +877,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,19 +906,25 @@
         <v>500</v>
       </c>
       <c r="K12" s="3">
+        <v>500</v>
+      </c>
+      <c r="L12" s="3">
+        <v>500</v>
+      </c>
+      <c r="M12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -928,8 +961,14 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -954,11 +993,11 @@
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -966,35 +1005,41 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1004,8 +1049,14 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1017,60 +1068,68 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F17" s="3">
         <v>1300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="N17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="H17" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2100</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1200</v>
       </c>
       <c r="H18" s="3">
         <v>-1200</v>
@@ -1082,19 +1141,25 @@
         <v>-1200</v>
       </c>
       <c r="K18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1109,99 +1174,113 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F22" s="3">
         <v>500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
@@ -1214,63 +1293,75 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>16</v>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1299,8 +1390,14 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1337,84 +1434,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1600</v>
       </c>
-      <c r="G26" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1451,8 +1566,14 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1489,8 +1610,14 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1527,8 +1654,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1565,84 +1698,102 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="G33" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1679,89 +1830,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="G35" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1776,8 +1945,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1792,46 +1963,54 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F41" s="3">
         <v>9700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>9700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8400</v>
       </c>
-      <c r="G41" s="3">
-        <v>7900</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J41" s="3">
         <v>10600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1868,84 +2047,102 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>900</v>
+      </c>
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1000</v>
       </c>
-      <c r="G43" s="3">
-        <v>900</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J43" s="3">
         <v>500</v>
-      </c>
-      <c r="I43" s="3">
-        <v>500</v>
-      </c>
-      <c r="J43" s="3">
-        <v>600</v>
       </c>
       <c r="K43" s="3">
         <v>500</v>
       </c>
       <c r="L43" s="3">
+        <v>600</v>
+      </c>
+      <c r="M43" s="3">
+        <v>500</v>
+      </c>
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>900</v>
+      </c>
+      <c r="F44" s="3">
         <v>700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1982,46 +2179,58 @@
       <c r="N45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F46" s="3">
         <v>10900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10900</v>
       </c>
-      <c r="F46" s="3">
-        <v>10300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>9800</v>
-      </c>
       <c r="H46" s="3">
+        <v>10400</v>
+      </c>
+      <c r="I46" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J46" s="3">
         <v>11900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>14000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2046,11 +2255,11 @@
       <c r="J47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2058,46 +2267,58 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>300</v>
+      </c>
+      <c r="F48" s="3">
         <v>400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2134,8 +2355,14 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2172,8 +2399,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2210,8 +2443,14 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2236,11 +2475,11 @@
       <c r="J52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2248,8 +2487,14 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2286,46 +2531,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F54" s="3">
         <v>11300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>11300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>10900</v>
       </c>
-      <c r="G54" s="3">
-        <v>10300</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
+        <v>10900</v>
+      </c>
+      <c r="J54" s="3">
         <v>12200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>12300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>14400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>5200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2340,8 +2597,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2356,8 +2615,10 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2368,34 +2629,40 @@
         <v>300</v>
       </c>
       <c r="F57" s="3">
+        <v>300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>300</v>
+      </c>
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2430,132 +2697,156 @@
         <v>200</v>
       </c>
       <c r="N58" s="3">
+        <v>200</v>
+      </c>
+      <c r="O58" s="3">
+        <v>200</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
         <v>2300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2300</v>
       </c>
-      <c r="F59" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1900</v>
-      </c>
       <c r="H59" s="3">
+        <v>900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>900</v>
+      </c>
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1600</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F60" s="3">
         <v>2800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>2600</v>
-      </c>
       <c r="H60" s="3">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="I60" s="3">
-        <v>2100</v>
+        <v>1600</v>
       </c>
       <c r="J60" s="3">
         <v>2100</v>
       </c>
       <c r="K60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="M60" s="3">
         <v>1000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>200</v>
-      </c>
-      <c r="H61" s="3">
-        <v>100</v>
-      </c>
-      <c r="I61" s="3">
-        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>100</v>
       </c>
       <c r="K61" s="3">
+        <v>100</v>
+      </c>
+      <c r="L61" s="3">
+        <v>100</v>
+      </c>
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>16</v>
+      <c r="D62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5100</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>16</v>
@@ -2563,20 +2854,20 @@
       <c r="G62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>16</v>
+      <c r="H62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1100</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K62" s="3">
-        <v>500</v>
-      </c>
-      <c r="L62" s="3">
-        <v>500</v>
+      <c r="K62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M62" s="3">
         <v>500</v>
@@ -2584,8 +2875,14 @@
       <c r="N62" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>500</v>
+      </c>
+      <c r="P62" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2622,8 +2919,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2660,8 +2963,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2698,46 +3007,58 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3100</v>
+        <v>6800</v>
       </c>
       <c r="E66" s="3">
-        <v>3100</v>
+        <v>6800</v>
       </c>
       <c r="F66" s="3">
         <v>3100</v>
       </c>
       <c r="G66" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="H66" s="3">
-        <v>2300</v>
+        <v>3200</v>
       </c>
       <c r="I66" s="3">
-        <v>2300</v>
+        <v>3200</v>
       </c>
       <c r="J66" s="3">
         <v>2300</v>
       </c>
       <c r="K66" s="3">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="L66" s="3">
-        <v>1700</v>
+        <v>2300</v>
       </c>
       <c r="M66" s="3">
         <v>1800</v>
       </c>
       <c r="N66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2752,8 +3073,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2790,8 +3113,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2828,8 +3157,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2866,8 +3201,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2904,46 +3245,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-24000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-24000</v>
       </c>
-      <c r="F72" s="3">
-        <v>-21100</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-20000</v>
-      </c>
       <c r="H72" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="J72" s="3">
         <v>-17400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-17600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-16300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-14400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-14000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-12900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2980,8 +3333,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3018,8 +3377,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3056,46 +3421,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F76" s="3">
         <v>8200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7700</v>
       </c>
-      <c r="G76" s="3">
-        <v>7300</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>7700</v>
+      </c>
+      <c r="J76" s="3">
         <v>9900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>12100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3132,89 +3509,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="G81" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3229,8 +3624,10 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3246,20 +3643,20 @@
       <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -3267,8 +3664,14 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3305,8 +3708,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3343,8 +3752,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3381,8 +3796,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3419,8 +3840,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3457,46 +3884,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-1300</v>
-      </c>
       <c r="H89" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="I89" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="J89" s="3">
         <v>-1100</v>
       </c>
       <c r="K89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M89" s="3">
         <v>-400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3511,8 +3950,10 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3549,8 +3990,14 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3587,8 +4034,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3625,8 +4078,14 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3661,10 +4120,16 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3679,8 +4144,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3705,11 +4172,11 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -3717,8 +4184,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3755,8 +4228,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3793,8 +4272,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3831,22 +4316,28 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>500</v>
+      </c>
+      <c r="F100" s="3">
         <v>1200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-100</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
@@ -3855,22 +4346,28 @@
         <v>-100</v>
       </c>
       <c r="J100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3">
         <v>6700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>2400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3880,11 +4377,11 @@
       <c r="E101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -3907,22 +4404,28 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-1200</v>
       </c>
       <c r="H102" s="3">
         <v>-1100</v>
@@ -3931,18 +4434,24 @@
         <v>-1100</v>
       </c>
       <c r="J102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L102" s="3">
         <v>5700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>MOB</t>
   </si>
@@ -656,81 +656,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -741,40 +749,46 @@
         <v>700</v>
       </c>
       <c r="F8" s="3">
+        <v>700</v>
+      </c>
+      <c r="G8" s="3">
+        <v>700</v>
+      </c>
+      <c r="H8" s="3">
         <v>900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -785,40 +799,46 @@
         <v>300</v>
       </c>
       <c r="F9" s="3">
+        <v>300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>300</v>
+      </c>
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>300</v>
-      </c>
-      <c r="J9" s="3">
-        <v>100</v>
-      </c>
-      <c r="K9" s="3">
-        <v>100</v>
       </c>
       <c r="L9" s="3">
         <v>100</v>
       </c>
       <c r="M9" s="3">
+        <v>100</v>
+      </c>
+      <c r="N9" s="3">
+        <v>100</v>
+      </c>
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -829,10 +849,10 @@
         <v>400</v>
       </c>
       <c r="F10" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G10" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H10" s="3">
         <v>500</v>
@@ -841,28 +861,34 @@
         <v>500</v>
       </c>
       <c r="J10" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="K10" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="L10" s="3">
         <v>200</v>
       </c>
       <c r="M10" s="3">
+        <v>200</v>
+      </c>
+      <c r="N10" s="3">
+        <v>200</v>
+      </c>
+      <c r="O10" s="3">
         <v>1200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -879,16 +905,18 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E12" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="F12" s="3">
         <v>500</v>
@@ -912,19 +940,25 @@
         <v>500</v>
       </c>
       <c r="M12" s="3">
+        <v>500</v>
+      </c>
+      <c r="N12" s="3">
+        <v>500</v>
+      </c>
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -967,8 +1001,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -999,11 +1039,11 @@
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1011,41 +1051,47 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1055,8 +1101,14 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,72 +1122,80 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>700</v>
+      </c>
+      <c r="F17" s="3">
         <v>2300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1200</v>
       </c>
       <c r="J18" s="3">
         <v>-1200</v>
@@ -1147,19 +1207,25 @@
         <v>-1200</v>
       </c>
       <c r="M18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1176,117 +1242,131 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>2100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-3700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>-500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>-500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
@@ -1299,76 +1379,88 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>16</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -1396,8 +1488,14 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1440,96 +1538,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1572,8 +1688,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1616,8 +1738,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1660,8 +1788,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1704,96 +1838,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1836,101 +1988,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1947,8 +2117,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1965,52 +2137,60 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F41" s="3">
         <v>8600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>12900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2053,96 +2233,114 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>700</v>
+      </c>
+      <c r="F43" s="3">
         <v>900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>500</v>
-      </c>
-      <c r="K43" s="3">
-        <v>500</v>
-      </c>
-      <c r="L43" s="3">
-        <v>600</v>
       </c>
       <c r="M43" s="3">
         <v>500</v>
       </c>
       <c r="N43" s="3">
+        <v>600</v>
+      </c>
+      <c r="O43" s="3">
+        <v>500</v>
+      </c>
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="3">
         <v>900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2185,52 +2383,64 @@
       <c r="P45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F46" s="3">
         <v>10500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>11900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>11900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>14000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>2400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2261,11 +2471,11 @@
       <c r="L47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2273,52 +2483,64 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>600</v>
+      </c>
+      <c r="F48" s="3">
         <v>300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2361,8 +2583,14 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2405,8 +2633,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2449,8 +2683,14 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2481,11 +2721,11 @@
       <c r="L52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -2493,8 +2733,14 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2537,52 +2783,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F54" s="3">
         <v>10800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>12200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>12300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>14400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>5200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>3100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>3900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2599,8 +2857,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2617,16 +2877,18 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>300</v>
@@ -2635,34 +2897,40 @@
         <v>300</v>
       </c>
       <c r="H57" s="3">
+        <v>300</v>
+      </c>
+      <c r="I57" s="3">
+        <v>300</v>
+      </c>
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2703,177 +2971,201 @@
         <v>200</v>
       </c>
       <c r="P58" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>200</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>800</v>
+      </c>
+      <c r="F59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>16</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F60" s="3">
         <v>1400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1600</v>
-      </c>
-      <c r="J60" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K60" s="3">
-        <v>2100</v>
       </c>
       <c r="L60" s="3">
         <v>2100</v>
       </c>
       <c r="M60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O60" s="3">
         <v>1000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>200</v>
-      </c>
-      <c r="J61" s="3">
-        <v>100</v>
-      </c>
-      <c r="K61" s="3">
-        <v>100</v>
       </c>
       <c r="L61" s="3">
         <v>100</v>
       </c>
       <c r="M61" s="3">
+        <v>100</v>
+      </c>
+      <c r="N61" s="3">
+        <v>100</v>
+      </c>
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F62" s="3">
         <v>5100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>5100</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="3">
         <v>1100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M62" s="3">
-        <v>500</v>
-      </c>
-      <c r="N62" s="3">
-        <v>500</v>
+      <c r="M62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O62" s="3">
         <v>500</v>
@@ -2881,8 +3173,14 @@
       <c r="P62" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>500</v>
+      </c>
+      <c r="R62" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2925,8 +3223,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2969,8 +3273,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3013,52 +3323,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F66" s="3">
         <v>6800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3200</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2300</v>
       </c>
       <c r="L66" s="3">
         <v>2300</v>
       </c>
       <c r="M66" s="3">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="N66" s="3">
-        <v>1700</v>
+        <v>2300</v>
       </c>
       <c r="O66" s="3">
         <v>1800</v>
       </c>
       <c r="P66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3075,8 +3397,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3119,8 +3443,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3163,8 +3493,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3207,8 +3543,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3251,52 +3593,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-30400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-30400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-24000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-24000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-22400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-22400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-17400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-17600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-16300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-14400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-14000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-12900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3339,8 +3693,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3383,8 +3743,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3427,52 +3793,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F76" s="3">
         <v>4000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>8200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>10000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>12100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>2200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3515,101 +3893,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3626,8 +4022,10 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3649,20 +4047,20 @@
       <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -3670,8 +4068,14 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3714,8 +4118,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3758,8 +4168,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3802,8 +4218,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3846,8 +4268,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3890,52 +4318,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1100</v>
       </c>
       <c r="L89" s="3">
         <v>-1100</v>
       </c>
       <c r="M89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="O89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3952,8 +4392,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3996,8 +4438,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4040,8 +4488,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4084,8 +4538,14 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4126,10 +4586,16 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4146,8 +4612,10 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4178,11 +4646,11 @@
       <c r="L96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -4190,8 +4658,14 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4234,8 +4708,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4278,8 +4758,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4322,28 +4808,34 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-100</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
@@ -4352,22 +4844,28 @@
         <v>-100</v>
       </c>
       <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
         <v>6700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2400</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4383,11 +4881,11 @@
       <c r="G101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
@@ -4410,28 +4908,34 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-1100</v>
       </c>
       <c r="J102" s="3">
         <v>-1100</v>
@@ -4440,18 +4944,24 @@
         <v>-1100</v>
       </c>
       <c r="L102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="N102" s="3">
         <v>5700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>2000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MOB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>MOB</t>
   </si>
@@ -656,97 +656,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E8" s="3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="3">
         <v>700</v>
@@ -755,48 +762,54 @@
         <v>700</v>
       </c>
       <c r="H8" s="3">
+        <v>700</v>
+      </c>
+      <c r="I8" s="3">
+        <v>700</v>
+      </c>
+      <c r="J8" s="3">
         <v>900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E9" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F9" s="3">
         <v>300</v>
@@ -805,48 +818,54 @@
         <v>300</v>
       </c>
       <c r="H9" s="3">
+        <v>300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>300</v>
+      </c>
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>300</v>
-      </c>
-      <c r="L9" s="3">
-        <v>100</v>
-      </c>
-      <c r="M9" s="3">
-        <v>100</v>
       </c>
       <c r="N9" s="3">
         <v>100</v>
       </c>
       <c r="O9" s="3">
+        <v>100</v>
+      </c>
+      <c r="P9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E10" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F10" s="3">
         <v>400</v>
@@ -855,10 +874,10 @@
         <v>400</v>
       </c>
       <c r="H10" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I10" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J10" s="3">
         <v>500</v>
@@ -867,28 +886,34 @@
         <v>500</v>
       </c>
       <c r="L10" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="M10" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="N10" s="3">
         <v>200</v>
       </c>
       <c r="O10" s="3">
+        <v>200</v>
+      </c>
+      <c r="P10" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -907,22 +932,24 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F12" s="3">
         <v>700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>500</v>
       </c>
       <c r="H12" s="3">
         <v>500</v>
@@ -946,19 +973,25 @@
         <v>500</v>
       </c>
       <c r="O12" s="3">
+        <v>500</v>
+      </c>
+      <c r="P12" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q12" s="3">
         <v>700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1007,8 +1040,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,11 +1084,11 @@
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1057,47 +1096,53 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1107,8 +1152,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1124,84 +1175,92 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F17" s="3">
         <v>700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-1200</v>
       </c>
       <c r="L18" s="3">
         <v>-1200</v>
@@ -1213,19 +1272,25 @@
         <v>-1200</v>
       </c>
       <c r="O18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1244,108 +1309,122 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>2100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-12000</v>
       </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-3700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-3700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1356,23 +1435,23 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>-500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>-500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>500</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1385,67 +1464,79 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>16</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-11900</v>
       </c>
       <c r="E23" s="3">
-        <v>0</v>
+        <v>-11900</v>
       </c>
       <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-3100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1456,17 +1547,17 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1494,8 +1585,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1544,108 +1641,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="E26" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="E27" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-3200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1694,8 +1809,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1744,8 +1865,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1794,8 +1921,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1844,108 +1977,126 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="E33" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1994,113 +2145,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="E35" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2119,8 +2288,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2139,58 +2310,66 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F41" s="3">
         <v>6800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>9700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>10700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2239,108 +2418,126 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>500</v>
-      </c>
-      <c r="M43" s="3">
-        <v>500</v>
-      </c>
-      <c r="N43" s="3">
-        <v>600</v>
       </c>
       <c r="O43" s="3">
         <v>500</v>
       </c>
       <c r="P43" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>500</v>
+      </c>
+      <c r="R43" s="3">
         <v>300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>700</v>
+      </c>
+      <c r="F44" s="3">
         <v>1000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2389,58 +2586,70 @@
       <c r="R45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>20200</v>
+      </c>
+      <c r="F46" s="3">
         <v>8600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>10400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>11900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>14000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>2400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2477,11 +2686,11 @@
       <c r="N47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2489,58 +2698,70 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>500</v>
+      </c>
+      <c r="F48" s="3">
         <v>600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2589,8 +2810,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2639,8 +2866,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2689,8 +2922,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2727,11 +2966,11 @@
       <c r="N52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -2739,8 +2978,14 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2789,58 +3034,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F54" s="3">
         <v>9200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>9200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>10800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>10800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>11300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>10900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>12200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>12300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>14400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>3100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>3900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2859,8 +3116,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2879,22 +3138,24 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>300</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
-      </c>
-      <c r="F57" s="3">
-        <v>300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>300</v>
       </c>
       <c r="H57" s="3">
         <v>300</v>
@@ -2903,34 +3164,40 @@
         <v>300</v>
       </c>
       <c r="J57" s="3">
+        <v>300</v>
+      </c>
+      <c r="K57" s="3">
+        <v>300</v>
+      </c>
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2977,201 +3244,225 @@
         <v>200</v>
       </c>
       <c r="R58" s="3">
+        <v>200</v>
+      </c>
+      <c r="S58" s="3">
+        <v>200</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F59" s="3">
         <v>800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F60" s="3">
         <v>1200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1600</v>
-      </c>
-      <c r="L60" s="3">
-        <v>2100</v>
-      </c>
-      <c r="M60" s="3">
-        <v>2100</v>
       </c>
       <c r="N60" s="3">
         <v>2100</v>
       </c>
       <c r="O60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P60" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>200</v>
+      </c>
+      <c r="F61" s="3">
         <v>300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>200</v>
-      </c>
-      <c r="L61" s="3">
-        <v>100</v>
-      </c>
-      <c r="M61" s="3">
-        <v>100</v>
       </c>
       <c r="N61" s="3">
         <v>100</v>
       </c>
       <c r="O61" s="3">
+        <v>100</v>
+      </c>
+      <c r="P61" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F62" s="3">
         <v>2600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>5100</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L62" s="3">
         <v>1100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O62" s="3">
-        <v>500</v>
-      </c>
-      <c r="P62" s="3">
-        <v>500</v>
+      <c r="O62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q62" s="3">
         <v>500</v>
@@ -3179,8 +3470,14 @@
       <c r="R62" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>500</v>
+      </c>
+      <c r="T62" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3229,8 +3526,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3279,8 +3582,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3329,58 +3638,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F66" s="3">
         <v>4400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3200</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M66" s="3">
-        <v>2300</v>
       </c>
       <c r="N66" s="3">
         <v>2300</v>
       </c>
       <c r="O66" s="3">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="P66" s="3">
-        <v>1700</v>
+        <v>2300</v>
       </c>
       <c r="Q66" s="3">
         <v>1800</v>
       </c>
       <c r="R66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T66" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3399,8 +3720,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3449,8 +3772,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3499,8 +3828,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3549,8 +3884,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3599,58 +3940,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="F72" s="3">
         <v>-30500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-30500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-30400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-30400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-24000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-24000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-22400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-22400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-17400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-17600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-16300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-14400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-12900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-11900</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3699,8 +4052,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3749,8 +4108,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3799,58 +4164,70 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F76" s="3">
         <v>4800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>10000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>12100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>2200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3899,113 +4276,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="E81" s="3">
-        <v>0</v>
+        <v>-11800</v>
       </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1400</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4024,8 +4419,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4053,20 +4450,20 @@
       <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="M83" s="3">
+        <v>100</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -4074,8 +4471,14 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4124,8 +4527,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4174,8 +4583,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4224,8 +4639,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4274,8 +4695,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4324,58 +4751,70 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-1100</v>
       </c>
       <c r="N89" s="3">
         <v>-1100</v>
       </c>
       <c r="O89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4394,8 +4833,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4444,8 +4885,14 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4494,8 +4941,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4544,8 +4997,14 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4592,10 +5051,16 @@
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4614,8 +5079,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4652,11 +5119,11 @@
       <c r="N96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4664,8 +5131,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4714,8 +5187,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4764,8 +5243,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4814,34 +5299,40 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1200</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
@@ -4850,22 +5341,28 @@
         <v>-100</v>
       </c>
       <c r="N100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P100" s="3">
         <v>6700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>2400</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4887,11 +5384,11 @@
       <c r="I101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="J101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4914,34 +5411,40 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-1100</v>
       </c>
       <c r="L102" s="3">
         <v>-1100</v>
@@ -4950,18 +5453,24 @@
         <v>-1100</v>
       </c>
       <c r="N102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="O102" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P102" s="3">
         <v>5700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>2000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1400</v>
       </c>
     </row>
